--- a/SAKHALIN_ZAPROS/01_ООО_ЧелябинскСпецГражданСтрой.xlsx
+++ b/SAKHALIN_ZAPROS/01_ООО_ЧелябинскСпецГражданСтрой.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -692,7 +692,7 @@
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -825,11 +825,11 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Кран шаровый LD КШЦП из стали 20 Ду25 Ру4,0МПа</t>
+          <t>Кран шаровый LD КШЦП из стали 20 Ду20 Ру4,0МПа</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой LD КШ.Ц.П.025.040.Н/П.02 (ст.20, Ду25, Ру4,0 МПа, под приварку)</t>
+          <t>Кран шаровой LD КШ.Ц.П.020.040.Н/П.02 (ст.20, Ду20, Ру4,0 МПа, под приварку)</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -887,15 +887,15 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Кран шаровый LD КШЦП из стали 20 Ду50 Ру4,0МПа</t>
+          <t>Кран шаровый LD КШЦП из стали 20 Ду20 Ру4,0МПа</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой LD КШ.Ц.П.050.040.Н/П.02 (ст.20, Ду50, Ру4,0 МПа, под приварку)</t>
+          <t>Кран шаровой LD КШ.Ц.П.020.040.Н/П.02 (ст.20, Ду20, Ру4,0 МПа, под приварку)</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -940,7 +940,7 @@
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -949,15 +949,15 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Кран шаровый Стандарт 1/2" ВВ бабочка VALTEC Артикул:VT. 122. GN. 04</t>
+          <t>Кран шаровый LD КШЦП из стали 20 Ду25 Ру4,0МПа</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Кран шаровой LD Pride 47.15.В-В.Б 1/2" (ВР-ВР, бабочка)</t>
+          <t>Кран шаровой LD КШ.Ц.П.025.040.Н/П.02 (ст.20, Ду25, Ру4,0 МПа, под приварку)</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1011,26 +1011,46 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Фланец ГОСТ 33259-2015 (ГОСТ 12820-80)  Ду 200 Ру 16 исп.B (1исп.)</t>
+          <t>Кран шаровый LD КШЦП из стали 20 Ду32 Ру4,0МПа</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="8" t="n"/>
-      <c r="K11" s="8" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Кран шаровой LD КШ.Ц.П.032.040.Н/П.02 (ст.20, Ду32, Ру4,0 МПа, под приварку)</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (завод LD / LD Pride; продажи — ООО «ТД «ЛД»)</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="L11" s="8" t="n"/>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="10">
@@ -1044,7 +1064,7 @@
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1053,26 +1073,46 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Фланец ГОСТ 33259-2015 (ГОСТ 12820-80)  Ду 32 Ру 10 исп.B (1исп.)</t>
+          <t>Кран шаровый LD КШЦП из стали 20 Ду50 Ру4,0МПа</t>
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
-      <c r="K12" s="8" t="n"/>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Кран шаровой LD КШ.Ц.П.050.040.Н/П.02 (ст.20, Ду50, Ру4,0 МПа, под приварку)</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (завод LD / LD Pride; продажи — ООО «ТД «ЛД»)</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="L12" s="8" t="n"/>
       <c r="M12" s="9" t="n"/>
       <c r="N12" s="10">
@@ -1086,7 +1126,7 @@
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1095,26 +1135,46 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Фланец ГОСТ 33259-2015 (ГОСТ 12820-80)  Ду 50 Ру 10 исп.B (1исп.)</t>
+          <t>Кран шаровый LD КШЦП из стали 20 Ду50 Ру4,0МПа</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="8" t="n"/>
-      <c r="J13" s="8" t="n"/>
-      <c r="K13" s="8" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Кран шаровой LD КШ.Ц.П.050.040.Н/П.02 (ст.20, Ду50, Ру4,0 МПа, под приварку)</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (завод LD / LD Pride; продажи — ООО «ТД «ЛД»)</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="L13" s="8" t="n"/>
       <c r="M13" s="9" t="n"/>
       <c r="N13" s="10">
@@ -1128,7 +1188,7 @@
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1137,15 +1197,15 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Фланец ГОСТ 33259-2015 (ГОСТ 12820-80)  Ду 80 Ру 10 исп.B (1исп.)</t>
+          <t>Кран шаровой VALTEC BASE, рукоятка 3/4" вн.-вн. VT.214.N.05</t>
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -1170,7 +1230,7 @@
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1179,15 +1239,15 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Фланец ГОСТ 33259-2015 (ГОСТ 12820-80)  Ду 100 Ру 10 исп.B (1исп.)</t>
+          <t>Кран шаровой VALTEC BASE, рукоятка 2" вн.-вн.VT.214.N.09</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -1212,7 +1272,7 @@
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1221,11 +1281,11 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Фланец ГОСТ 33259-2015 (ГОСТ 12820-80)  Ду 150 Ру 10 исп.B (1исп.)</t>
+          <t>Кран шаровой VALTEC BASE, рукоятка 1" вн.-вн. VT.214.N.06</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
@@ -1254,35 +1314,55 @@
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>№ 2</t>
+          <t>№ 1</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Фланец ГОСТ 33259-2015 (ГОСТ 12820-80)   Ду 50 Ру 10 исп.B (1исп.)</t>
+          <t>Кран шаровый Стандарт 1/2" ВВ бабочка VALTEC Артикул:VT. 122. GN. 04</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="8" t="n"/>
-      <c r="K17" s="8" t="n"/>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Кран шаровой LD Pride 47.15.В-В.Б 1/2" (ВР-ВР, бабочка)</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (завод LD / LD Pride; продажи — ООО «ТД «ЛД»)</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="L17" s="8" t="n"/>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="10">
@@ -1296,24 +1376,24 @@
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>№ 2</t>
+          <t>№ 1</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Кран шаровый стальной ALSO Ду-80; Ру-16 фланцевый полнопроходной Сталь 20 под задвижку</t>
+          <t>Кран шаровый муфтовый 11б27п1 Ду 15 Ру 16</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -1338,35 +1418,55 @@
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>№ 3</t>
+          <t>№ 1</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Кран шаровый муфтовый 11б27п1 Ду 15 Ру 16 Кран шаровый муфтовый 11б27п1 Ду 15 Ру 16</t>
+          <t>Кран шаровый LD Ду 80 Ру 25 фланцевый стальной КШ.Ц.Ф.080/070.025.Н/П.02</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Кран шаровой LD КШ.Ц.Ф.080/070.025.Н/П.02 (Ду80, Ру25, фланцевый, ст.20)</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (завод LD / LD Pride; продажи — ООО «ТД «ЛД»)</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
       <c r="L19" s="8" t="n"/>
       <c r="M19" s="9" t="n"/>
       <c r="N19" s="10">
@@ -1380,12 +1480,12 @@
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>№ 3</t>
+          <t>№ 2</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
@@ -1393,11 +1493,11 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Кран шаровый муфтовый  11б27п1 Ду 20 Ру 16 Кран шаровый муфтовый  11б27п1 Ду 20 Ру 16</t>
+          <t>Кран шаровой VALTEC BASE, рукоятка 3/4" вн.-вн. VT.214.N.05</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -1427,50 +1527,30 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>№ 1</t>
+          <t>№ 2</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Кран шаровый LD КШЦП из стали 20 Ду15 Ру4,0МПа</t>
+          <t>Кран шаровый муфтовый 11б27п1 Ду 15 Ру 16</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Кран шаровой LD КШ.Ц.П.015.040.Н/П.02 (ст.20, Ду15, Ру4,0 МПа, под приварку)</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» (завод LD / LD Pride; продажи — ООО «ТД «ЛД»)</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>10655491</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>30.06.2028</t>
-        </is>
-      </c>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="8" t="n"/>
+      <c r="K21" s="8" t="n"/>
       <c r="L21" s="8" t="n"/>
       <c r="M21" s="9" t="n"/>
       <c r="N21" s="10">
@@ -1489,50 +1569,30 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>№ 1</t>
+          <t>№ 2</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Кран шаровый LD КШЦП из стали 20 Ду20 Ру4,0МПа</t>
+          <t>Кран шаровый муфтовый  11б27п1 Ду 20 Ру 16</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>Кран шаровой LD КШ.Ц.П.020.040.Н/П.02 (ст.20, Ду20, Ру4,0 МПа, под приварку)</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» (завод LD / LD Pride; продажи — ООО «ТД «ЛД»)</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>10655491</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>30.06.2028</t>
-        </is>
-      </c>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="9" t="n"/>
       <c r="N22" s="10">
@@ -1551,50 +1611,30 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>№ 1</t>
+          <t>№ 2</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Кран шаровый LD КШЦП из стали 20 Ду20 Ру4,0МПа</t>
+          <t>Кран шаровый с характеристиками не ниже и отвечающий техническим требованиям: размер 1/2", 150гр.Ц, полнопроходной, корпус латунный, никелированный, резьба внутренняя/наружная. Либо VALTEC BAS VT.218.N.04</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Кран шаровой LD КШ.Ц.П.020.040.Н/П.02 (ст.20, Ду20, Ру4,0 МПа, под приварку)</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» (завод LD / LD Pride; продажи — ООО «ТД «ЛД»)</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>10655491</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>30.06.2028</t>
-        </is>
-      </c>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
       <c r="L23" s="8" t="n"/>
       <c r="M23" s="9" t="n"/>
       <c r="N23" s="10">
@@ -1613,50 +1653,30 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>№ 1</t>
+          <t>№ 2</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Кран шаровый LD КШЦП из стали 20 Ду20 Ру4,0МПа</t>
+          <t>Кран шаровый с характеристиками не ниже и отвечающий техническим требованиям: размер 3/4", 150 гр.Ц, полнопроходной, корпус латунный, никелированный, резьба внутренняя/наружная. Либо VALTEC BAS VT.218.N.05</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>Кран шаровой LD КШ.Ц.П.020.040.Н/П.02 (ст.20, Ду20, Ру4,0 МПа, под приварку)</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» (завод LD / LD Pride; продажи — ООО «ТД «ЛД»)</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>10655491</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="inlineStr">
-        <is>
-          <t>30.06.2028</t>
-        </is>
-      </c>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="9" t="n"/>
       <c r="N24" s="10">
@@ -1675,50 +1695,30 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>№ 1</t>
+          <t>№ 2</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Кран шаровый LD КШЦП из стали 20 Ду25 Ру4,0МПа</t>
+          <t>Кран шаровый с характеристиками не ниже и отвечающий техническим требованиям: размер 1/2", 150гр.Ц, полнопроходной, корпус латунный, никелированный, с полусгоном и наружной резьбой. Либо VALTEC BAS VT.226.N.04</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>Кран шаровой LD КШ.Ц.П.025.040.Н/П.02 (ст.20, Ду25, Ру4,0 МПа, под приварку)</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» (завод LD / LD Pride; продажи — ООО «ТД «ЛД»)</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>10655491</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="inlineStr">
-        <is>
-          <t>30.06.2028</t>
-        </is>
-      </c>
+      <c r="G25" s="8" t="n"/>
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="8" t="n"/>
+      <c r="J25" s="8" t="n"/>
+      <c r="K25" s="8" t="n"/>
       <c r="L25" s="8" t="n"/>
       <c r="M25" s="9" t="n"/>
       <c r="N25" s="10">
@@ -1737,50 +1737,30 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>№ 1</t>
+          <t>№ 2</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Кран шаровый LD КШЦП из стали 20 Ду32 Ру4,0МПа</t>
+          <t>Кран шаровый с характеристиками не ниже и отвечающий техническим требованиям: размер 3/4", 150гр.Ц , полнопроходной, корпус латунный, никелированный, с полусгоном и наружной резьбой. Либо VALTEC BAS VT.226.N.05</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>Кран шаровой LD КШ.Ц.П.032.040.Н/П.02 (ст.20, Ду32, Ру4,0 МПа, под приварку)</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» (завод LD / LD Pride; продажи — ООО «ТД «ЛД»)</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>10655491</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>30.06.2028</t>
-        </is>
-      </c>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
       <c r="L26" s="8" t="n"/>
       <c r="M26" s="9" t="n"/>
       <c r="N26" s="10">
@@ -1799,50 +1779,30 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>№ 1</t>
+          <t>№ 2</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Кран шаровый LD КШЦП из стали 20 Ду50 Ру4,0МПа</t>
+          <t>Кран шаровой ГАЛЛОП Практик 120 1″ Ду25 Ру16 стандартнопроходной,</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>Кран шаровой LD КШ.Ц.П.050.040.Н/П.02 (ст.20, Ду50, Ру4,0 МПа, под приварку)</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» (завод LD / LD Pride; продажи — ООО «ТД «ЛД»)</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>10655491</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>30.06.2028</t>
-        </is>
-      </c>
+      <c r="G27" s="8" t="n"/>
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="8" t="n"/>
+      <c r="J27" s="8" t="n"/>
+      <c r="K27" s="8" t="n"/>
       <c r="L27" s="8" t="n"/>
       <c r="M27" s="9" t="n"/>
       <c r="N27" s="10">
@@ -1854,762 +1814,30 @@
       <c r="Q27" s="8" t="n"/>
     </row>
     <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>№ 1</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Кран шаровый LD КШЦП из стали 20 Ду50 Ру4,0МПа</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>Кран шаровой LD КШ.Ц.П.050.040.Н/П.02 (ст.20, Ду50, Ру4,0 МПа, под приварку)</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» (завод LD / LD Pride; продажи — ООО «ТД «ЛД»)</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>10655491</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>30.06.2028</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="n"/>
-      <c r="M28" s="9" t="n"/>
-      <c r="N28" s="10">
-        <f>M28*E28</f>
-        <v/>
-      </c>
-      <c r="O28" s="8" t="n"/>
-      <c r="P28" s="8" t="n"/>
-      <c r="Q28" s="8" t="n"/>
-    </row>
-    <row r="29" ht="48" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>№ 1</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Кран шаровой VALTEC BASE, рукоятка 3/4" вн.-вн. VT.214.N.05</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="8" t="n"/>
-      <c r="L29" s="8" t="n"/>
-      <c r="M29" s="9" t="n"/>
-      <c r="N29" s="10">
-        <f>M29*E29</f>
-        <v/>
-      </c>
-      <c r="O29" s="8" t="n"/>
-      <c r="P29" s="8" t="n"/>
-      <c r="Q29" s="8" t="n"/>
-    </row>
-    <row r="30" ht="48" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>№ 1</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Кран шаровой VALTEC BASE, рукоятка 2" вн.-вн.VT.214.N.09</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="n"/>
-      <c r="J30" s="8" t="n"/>
-      <c r="K30" s="8" t="n"/>
-      <c r="L30" s="8" t="n"/>
-      <c r="M30" s="9" t="n"/>
-      <c r="N30" s="10">
-        <f>M30*E30</f>
-        <v/>
-      </c>
-      <c r="O30" s="8" t="n"/>
-      <c r="P30" s="8" t="n"/>
-      <c r="Q30" s="8" t="n"/>
-    </row>
-    <row r="31" ht="48" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>№ 1</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Кран шаровой VALTEC BASE, рукоятка 1" вн.-вн. VT.214.N.06</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="n"/>
-      <c r="J31" s="8" t="n"/>
-      <c r="K31" s="8" t="n"/>
-      <c r="L31" s="8" t="n"/>
-      <c r="M31" s="9" t="n"/>
-      <c r="N31" s="10">
-        <f>M31*E31</f>
-        <v/>
-      </c>
-      <c r="O31" s="8" t="n"/>
-      <c r="P31" s="8" t="n"/>
-      <c r="Q31" s="8" t="n"/>
-    </row>
-    <row r="32" ht="48" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>№ 1</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Кран шаровый Стандарт 1/2" ВВ бабочка VALTEC Артикул:VT. 122. GN. 04</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>Кран шаровой LD Pride 47.15.В-В.Б 1/2" (ВР-ВР, бабочка)</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» (завод LD / LD Pride; продажи — ООО «ТД «ЛД»)</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>10655491</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>30.06.2028</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="n"/>
-      <c r="M32" s="9" t="n"/>
-      <c r="N32" s="10">
-        <f>M32*E32</f>
-        <v/>
-      </c>
-      <c r="O32" s="8" t="n"/>
-      <c r="P32" s="8" t="n"/>
-      <c r="Q32" s="8" t="n"/>
-    </row>
-    <row r="33" ht="48" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>№ 1</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Кран шаровый муфтовый 11б27п1 Ду 15 Ру 16</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
-      <c r="K33" s="8" t="n"/>
-      <c r="L33" s="8" t="n"/>
-      <c r="M33" s="9" t="n"/>
-      <c r="N33" s="10">
-        <f>M33*E33</f>
-        <v/>
-      </c>
-      <c r="O33" s="8" t="n"/>
-      <c r="P33" s="8" t="n"/>
-      <c r="Q33" s="8" t="n"/>
-    </row>
-    <row r="34" ht="48" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>№ 1</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Кран шаровый LD Ду 80 Ру 25 фланцевый стальной КШ.Ц.Ф.080/070.025.Н/П.02</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>Кран шаровой LD КШ.Ц.Ф.080/070.025.Н/П.02 (Ду80, Ру25, фланцевый, ст.20)</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» (завод LD / LD Pride; продажи — ООО «ТД «ЛД»)</t>
-        </is>
-      </c>
-      <c r="I34" s="7" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="J34" s="7" t="inlineStr">
-        <is>
-          <t>10655491</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="inlineStr">
-        <is>
-          <t>30.06.2028</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="n"/>
-      <c r="M34" s="9" t="n"/>
-      <c r="N34" s="10">
-        <f>M34*E34</f>
-        <v/>
-      </c>
-      <c r="O34" s="8" t="n"/>
-      <c r="P34" s="8" t="n"/>
-      <c r="Q34" s="8" t="n"/>
-    </row>
-    <row r="35" ht="48" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>№ 1</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="n">
-        <v>69</v>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Кран шаровый полнопроходной Классик ФБ39.210.050.000-02 DN50 PN4МПа Ст20 -40...+160C кл.А У1 фланцевый 230мм</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="n"/>
-      <c r="I35" s="8" t="n"/>
-      <c r="J35" s="8" t="n"/>
-      <c r="K35" s="8" t="n"/>
-      <c r="L35" s="8" t="n"/>
-      <c r="M35" s="9" t="n"/>
-      <c r="N35" s="10">
-        <f>M35*E35</f>
-        <v/>
-      </c>
-      <c r="O35" s="8" t="n"/>
-      <c r="P35" s="8" t="n"/>
-      <c r="Q35" s="8" t="n"/>
-    </row>
-    <row r="36" ht="48" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>№ 2</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Кран шаровой VALTEC BASE, рукоятка 3/4" вн.-вн. VT.214.N.05</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="8" t="n"/>
-      <c r="J36" s="8" t="n"/>
-      <c r="K36" s="8" t="n"/>
-      <c r="L36" s="8" t="n"/>
-      <c r="M36" s="9" t="n"/>
-      <c r="N36" s="10">
-        <f>M36*E36</f>
-        <v/>
-      </c>
-      <c r="O36" s="8" t="n"/>
-      <c r="P36" s="8" t="n"/>
-      <c r="Q36" s="8" t="n"/>
-    </row>
-    <row r="37" ht="48" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>№ 2</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Кран шаровый муфтовый 11б27п1 Ду 15 Ру 16</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="n"/>
-      <c r="J37" s="8" t="n"/>
-      <c r="K37" s="8" t="n"/>
-      <c r="L37" s="8" t="n"/>
-      <c r="M37" s="9" t="n"/>
-      <c r="N37" s="10">
-        <f>M37*E37</f>
-        <v/>
-      </c>
-      <c r="O37" s="8" t="n"/>
-      <c r="P37" s="8" t="n"/>
-      <c r="Q37" s="8" t="n"/>
-    </row>
-    <row r="38" ht="48" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>№ 2</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>Кран шаровый муфтовый  11б27п1 Ду 20 Ру 16</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="8" t="n"/>
-      <c r="J38" s="8" t="n"/>
-      <c r="K38" s="8" t="n"/>
-      <c r="L38" s="8" t="n"/>
-      <c r="M38" s="9" t="n"/>
-      <c r="N38" s="10">
-        <f>M38*E38</f>
-        <v/>
-      </c>
-      <c r="O38" s="8" t="n"/>
-      <c r="P38" s="8" t="n"/>
-      <c r="Q38" s="8" t="n"/>
-    </row>
-    <row r="39" ht="48" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>№ 2</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Кран шаровый с характеристиками не ниже и отвечающий техническим требованиям: размер 1/2", 150гр.Ц, полнопроходной, корпус латунный, никелированный, резьба внутренняя/наружная. Либо VALTEC BAS VT.218.N.04</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="n"/>
-      <c r="I39" s="8" t="n"/>
-      <c r="J39" s="8" t="n"/>
-      <c r="K39" s="8" t="n"/>
-      <c r="L39" s="8" t="n"/>
-      <c r="M39" s="9" t="n"/>
-      <c r="N39" s="10">
-        <f>M39*E39</f>
-        <v/>
-      </c>
-      <c r="O39" s="8" t="n"/>
-      <c r="P39" s="8" t="n"/>
-      <c r="Q39" s="8" t="n"/>
-    </row>
-    <row r="40" ht="48" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>№ 2</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>Кран шаровый с характеристиками не ниже и отвечающий техническим требованиям: размер 3/4", 150 гр.Ц, полнопроходной, корпус латунный, никелированный, резьба внутренняя/наружная. Либо VALTEC BAS VT.218.N.05</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="8" t="n"/>
-      <c r="J40" s="8" t="n"/>
-      <c r="K40" s="8" t="n"/>
-      <c r="L40" s="8" t="n"/>
-      <c r="M40" s="9" t="n"/>
-      <c r="N40" s="10">
-        <f>M40*E40</f>
-        <v/>
-      </c>
-      <c r="O40" s="8" t="n"/>
-      <c r="P40" s="8" t="n"/>
-      <c r="Q40" s="8" t="n"/>
-    </row>
-    <row r="41" ht="48" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>№ 2</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Кран шаровый с характеристиками не ниже и отвечающий техническим требованиям: размер 1/2", 150гр.Ц, полнопроходной, корпус латунный, никелированный, с полусгоном и наружной резьбой. Либо VALTEC BAS VT.226.N.04</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="8" t="n"/>
-      <c r="J41" s="8" t="n"/>
-      <c r="K41" s="8" t="n"/>
-      <c r="L41" s="8" t="n"/>
-      <c r="M41" s="9" t="n"/>
-      <c r="N41" s="10">
-        <f>M41*E41</f>
-        <v/>
-      </c>
-      <c r="O41" s="8" t="n"/>
-      <c r="P41" s="8" t="n"/>
-      <c r="Q41" s="8" t="n"/>
-    </row>
-    <row r="42" ht="48" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>№ 2</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Кран шаровый с характеристиками не ниже и отвечающий техническим требованиям: размер 3/4", 150гр.Ц , полнопроходной, корпус латунный, никелированный, с полусгоном и наружной резьбой. Либо VALTEC BAS VT.226.N.05</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="8" t="n"/>
-      <c r="J42" s="8" t="n"/>
-      <c r="K42" s="8" t="n"/>
-      <c r="L42" s="8" t="n"/>
-      <c r="M42" s="9" t="n"/>
-      <c r="N42" s="10">
-        <f>M42*E42</f>
-        <v/>
-      </c>
-      <c r="O42" s="8" t="n"/>
-      <c r="P42" s="8" t="n"/>
-      <c r="Q42" s="8" t="n"/>
-    </row>
-    <row r="43" ht="48" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>№ 2</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Кран шаровой ГАЛЛОП Практик 120 1″ Ду25 Ру16 стандартнопроходной,</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="n"/>
-      <c r="H43" s="8" t="n"/>
-      <c r="I43" s="8" t="n"/>
-      <c r="J43" s="8" t="n"/>
-      <c r="K43" s="8" t="n"/>
-      <c r="L43" s="8" t="n"/>
-      <c r="M43" s="9" t="n"/>
-      <c r="N43" s="10">
-        <f>M43*E43</f>
-        <v/>
-      </c>
-      <c r="O43" s="8" t="n"/>
-      <c r="P43" s="8" t="n"/>
-      <c r="Q43" s="8" t="n"/>
-    </row>
-    <row r="44" ht="48" customHeight="1">
-      <c r="A44" s="11" t="inlineStr"/>
-      <c r="B44" s="11" t="inlineStr"/>
-      <c r="C44" s="11" t="inlineStr"/>
-      <c r="D44" s="11" t="inlineStr"/>
-      <c r="E44" s="11" t="inlineStr"/>
-      <c r="F44" s="11" t="inlineStr"/>
-      <c r="G44" s="11" t="inlineStr"/>
-      <c r="H44" s="11" t="inlineStr"/>
-      <c r="I44" s="11" t="inlineStr"/>
-      <c r="J44" s="11" t="inlineStr"/>
-      <c r="K44" s="11" t="inlineStr"/>
-      <c r="L44" s="11" t="inlineStr"/>
-      <c r="M44" s="11" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr"/>
+      <c r="B28" s="11" t="inlineStr"/>
+      <c r="C28" s="11" t="inlineStr"/>
+      <c r="D28" s="11" t="inlineStr"/>
+      <c r="E28" s="11" t="inlineStr"/>
+      <c r="F28" s="11" t="inlineStr"/>
+      <c r="G28" s="11" t="inlineStr"/>
+      <c r="H28" s="11" t="inlineStr"/>
+      <c r="I28" s="11" t="inlineStr"/>
+      <c r="J28" s="11" t="inlineStr"/>
+      <c r="K28" s="11" t="inlineStr"/>
+      <c r="L28" s="11" t="inlineStr"/>
+      <c r="M28" s="11" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="N44" s="12">
-        <f>SUM(N6:N43)</f>
-        <v/>
-      </c>
-      <c r="O44" s="2" t="n"/>
-      <c r="P44" s="2" t="n"/>
-      <c r="Q44" s="2" t="n"/>
+      <c r="N28" s="12">
+        <f>SUM(N6:N27)</f>
+        <v/>
+      </c>
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="n"/>
+      <c r="Q28" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
